--- a/Shedule/2025.xlsx
+++ b/Shedule/2025.xlsx
@@ -5,13 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Plan" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Tracker" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Job" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="DRF" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="DRF_Doubts" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="diif job details" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Yearly" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="336">
   <si>
     <t xml:space="preserve">Daily Plan</t>
   </si>
@@ -2009,7 +2009,9 @@
       <c r="F6" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="18"/>
+      <c r="G6" s="14" t="s">
+        <v>40</v>
+      </c>
       <c r="H6" s="15" t="s">
         <v>41</v>
       </c>

--- a/Shedule/2025.xlsx
+++ b/Shedule/2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Plan" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="336">
   <si>
     <t xml:space="preserve">Daily Plan</t>
   </si>
@@ -1207,7 +1207,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1308,19 +1308,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2535,8 +2523,12 @@
       <c r="D13" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="E13" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="22" t="n">
@@ -2548,8 +2540,12 @@
       <c r="D14" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="E14" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="22" t="n">
@@ -2561,8 +2557,12 @@
       <c r="D15" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="E15" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="22" t="n">
@@ -2574,8 +2574,12 @@
       <c r="D16" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="E16" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="22" t="n">
@@ -2587,8 +2591,12 @@
       <c r="D17" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
+      <c r="E17" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="22" t="n">
@@ -2600,8 +2608,12 @@
       <c r="D18" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
+      <c r="E18" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="22" t="n">
@@ -2613,8 +2625,12 @@
       <c r="D19" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
+      <c r="E19" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="22" t="n">
@@ -2626,8 +2642,12 @@
       <c r="D20" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
+      <c r="E20" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="22" t="n">
@@ -2639,8 +2659,12 @@
       <c r="D21" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
+      <c r="E21" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="22" t="n">
@@ -2652,8 +2676,12 @@
       <c r="D22" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="E22" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="22" t="n">
@@ -2665,8 +2693,12 @@
       <c r="D23" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="E23" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="22" t="n">
@@ -2678,8 +2710,12 @@
       <c r="D24" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
+      <c r="E24" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="n">
@@ -2691,8 +2727,12 @@
       <c r="D25" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
+      <c r="E25" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="22" t="n">
@@ -2704,8 +2744,12 @@
       <c r="D26" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
+      <c r="E26" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="n">
@@ -2717,8 +2761,12 @@
       <c r="D27" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
+      <c r="E27" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="22" t="n">
@@ -2730,8 +2778,12 @@
       <c r="D28" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+      <c r="E28" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="22" t="n">
@@ -2743,8 +2795,12 @@
       <c r="D29" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="E29" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="22" t="n">
@@ -2756,8 +2812,12 @@
       <c r="D30" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="E30" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="22" t="n">
@@ -2769,8 +2829,12 @@
       <c r="D31" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
+      <c r="E31" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="22" t="n">
@@ -4505,18 +4569,18 @@
   <dimension ref="B2:D12"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="25" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="5.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="62.19"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="25" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="5.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="62.19"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="8" width="11.53"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
@@ -4530,77 +4594,77 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="27" t="n">
+      <c r="B4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="D4" s="27"/>
+      <c r="D4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="27"/>
+      <c r="D5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="27"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="27"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4624,13 +4688,13 @@
   <dimension ref="B2:F35"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="29" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="29" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="29" width="37.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="29" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="29" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="29" width="32"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="29" width="9.14"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="37.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="26" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="26" width="25.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="26" width="32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="26" width="9.14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4651,461 +4715,461 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="30" t="n">
+      <c r="B3" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="28" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="30" t="n">
+      <c r="B4" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="28" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="28" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="28" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="28" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="28" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="28" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="28" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="28" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="28" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30" t="n">
+      <c r="B13" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="28" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="n">
+      <c r="B14" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="28" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="28" t="s">
         <v>287</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="28" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="28" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="28" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="27" t="s">
         <v>297</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="28" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="27" t="s">
         <v>301</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="28" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="28" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="27" t="s">
         <v>308</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="28" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="27" t="s">
         <v>297</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="28" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="27" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="27" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="27" t="n">
         <v>32</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="27" t="n">
         <v>33</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5136,41 +5200,41 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="29" t="s">
         <v>314</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C3" s="32" t="n">
+      <c r="C3" s="29" t="n">
         <v>29</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32" t="n">
+      <c r="D3" s="29"/>
+      <c r="E3" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="32"/>
+      <c r="F3" s="29"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4"/>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5213,14 +5277,14 @@
       <c r="C7" s="22" t="s">
         <v>321</v>
       </c>
-      <c r="D7" s="33" t="b">
+      <c r="D7" s="30" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="F7" s="33" t="b">
+      <c r="F7" s="30" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -5230,14 +5294,14 @@
       <c r="C8" s="22" t="s">
         <v>322</v>
       </c>
-      <c r="D8" s="33" t="b">
+      <c r="D8" s="30" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>321</v>
       </c>
-      <c r="F8" s="33" t="b">
+      <c r="F8" s="30" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -5246,27 +5310,27 @@
       <c r="B9" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32" t="n">
+      <c r="D9" s="29"/>
+      <c r="E9" s="29" t="n">
         <v>31</v>
       </c>
-      <c r="F9" s="32"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4"/>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5309,14 +5373,14 @@
       <c r="C13" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="D13" s="33" t="b">
+      <c r="D13" s="30" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>325</v>
       </c>
-      <c r="F13" s="33" t="b">
+      <c r="F13" s="30" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -5325,27 +5389,27 @@
       <c r="B14" s="4" t="n">
         <v>2027</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="29" t="n">
         <v>31</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32" t="n">
+      <c r="D14" s="29"/>
+      <c r="E14" s="29" t="n">
         <v>32</v>
       </c>
-      <c r="F14" s="32"/>
+      <c r="F14" s="29"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4"/>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5385,33 +5449,33 @@
       <c r="B18" s="4" t="n">
         <v>2028</v>
       </c>
-      <c r="C18" s="34" t="n">
+      <c r="C18" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="D18" s="34"/>
-      <c r="E18" s="32" t="n">
+      <c r="D18" s="31"/>
+      <c r="E18" s="29" t="n">
         <v>33</v>
       </c>
-      <c r="F18" s="32"/>
+      <c r="F18" s="29"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4"/>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="F19" s="29" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="4"/>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="32" t="s">
         <v>330</v>
       </c>
       <c r="D20" s="24" t="b">
@@ -5426,7 +5490,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="4"/>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="32" t="s">
         <v>331</v>
       </c>
       <c r="D21" s="24" t="b">
@@ -5458,27 +5522,27 @@
       <c r="B23" s="4" t="n">
         <v>2029</v>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="29" t="n">
         <v>33</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32" t="n">
+      <c r="D23" s="29"/>
+      <c r="E23" s="29" t="n">
         <v>34</v>
       </c>
-      <c r="F23" s="32"/>
+      <c r="F23" s="29"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4"/>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="F24" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5512,27 +5576,27 @@
       <c r="B27" s="4" t="n">
         <v>2030</v>
       </c>
-      <c r="C27" s="32" t="n">
+      <c r="C27" s="29" t="n">
         <v>34</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32" t="n">
+      <c r="D27" s="29"/>
+      <c r="E27" s="29" t="n">
         <v>35</v>
       </c>
-      <c r="F27" s="32"/>
+      <c r="F27" s="29"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4"/>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F28" s="32" t="s">
+      <c r="F28" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5568,27 +5632,27 @@
       <c r="B31" s="4" t="n">
         <v>2031</v>
       </c>
-      <c r="C31" s="32" t="n">
+      <c r="C31" s="29" t="n">
         <v>35</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32" t="n">
+      <c r="D31" s="29"/>
+      <c r="E31" s="29" t="n">
         <v>36</v>
       </c>
-      <c r="F31" s="32"/>
+      <c r="F31" s="29"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4"/>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="32" t="s">
+      <c r="E32" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F32" s="32" t="s">
+      <c r="F32" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5624,27 +5688,27 @@
       <c r="B35" s="4" t="n">
         <v>2032</v>
       </c>
-      <c r="C35" s="32" t="n">
+      <c r="C35" s="29" t="n">
         <v>36</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32" t="n">
+      <c r="D35" s="29"/>
+      <c r="E35" s="29" t="n">
         <v>37</v>
       </c>
-      <c r="F35" s="32"/>
+      <c r="F35" s="29"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4"/>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="32" t="s">
+      <c r="E36" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F36" s="32" t="s">
+      <c r="F36" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5678,27 +5742,27 @@
       <c r="B39" s="4" t="n">
         <v>2033</v>
       </c>
-      <c r="C39" s="32" t="n">
+      <c r="C39" s="29" t="n">
         <v>37</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32" t="n">
+      <c r="D39" s="29"/>
+      <c r="E39" s="29" t="n">
         <v>38</v>
       </c>
-      <c r="F39" s="32"/>
+      <c r="F39" s="29"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4"/>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="32" t="s">
+      <c r="E40" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F40" s="32" t="s">
+      <c r="F40" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5732,27 +5796,27 @@
       <c r="B43" s="4" t="n">
         <v>2034</v>
       </c>
-      <c r="C43" s="32" t="n">
+      <c r="C43" s="29" t="n">
         <v>38</v>
       </c>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32" t="n">
+      <c r="D43" s="29"/>
+      <c r="E43" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="F43" s="32"/>
+      <c r="F43" s="29"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4"/>
-      <c r="C44" s="32" t="s">
+      <c r="C44" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F44" s="32" t="s">
+      <c r="F44" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5786,27 +5850,27 @@
       <c r="B47" s="4" t="n">
         <v>2035</v>
       </c>
-      <c r="C47" s="32" t="n">
+      <c r="C47" s="29" t="n">
         <v>39</v>
       </c>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32" t="n">
+      <c r="D47" s="29"/>
+      <c r="E47" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="F47" s="32"/>
+      <c r="F47" s="29"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4"/>
-      <c r="C48" s="32" t="s">
+      <c r="C48" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E48" s="32" t="s">
+      <c r="E48" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F48" s="32" t="s">
+      <c r="F48" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5842,27 +5906,27 @@
       <c r="B51" s="4" t="n">
         <v>2036</v>
       </c>
-      <c r="C51" s="32" t="n">
+      <c r="C51" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32" t="n">
+      <c r="D51" s="29"/>
+      <c r="E51" s="29" t="n">
         <v>41</v>
       </c>
-      <c r="F51" s="32"/>
+      <c r="F51" s="29"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4"/>
-      <c r="C52" s="32" t="s">
+      <c r="C52" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D52" s="32" t="s">
+      <c r="D52" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E52" s="32" t="s">
+      <c r="E52" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F52" s="32" t="s">
+      <c r="F52" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5898,27 +5962,27 @@
       <c r="B55" s="4" t="n">
         <v>2037</v>
       </c>
-      <c r="C55" s="32" t="n">
+      <c r="C55" s="29" t="n">
         <v>41</v>
       </c>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32" t="n">
+      <c r="D55" s="29"/>
+      <c r="E55" s="29" t="n">
         <v>42</v>
       </c>
-      <c r="F55" s="32"/>
+      <c r="F55" s="29"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="4"/>
-      <c r="C56" s="32" t="s">
+      <c r="C56" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D56" s="32" t="s">
+      <c r="D56" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E56" s="32" t="s">
+      <c r="E56" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F56" s="32" t="s">
+      <c r="F56" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5952,27 +6016,27 @@
       <c r="B59" s="4" t="n">
         <v>2038</v>
       </c>
-      <c r="C59" s="32" t="n">
+      <c r="C59" s="29" t="n">
         <v>42</v>
       </c>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32" t="n">
+      <c r="D59" s="29"/>
+      <c r="E59" s="29" t="n">
         <v>43</v>
       </c>
-      <c r="F59" s="32"/>
+      <c r="F59" s="29"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4"/>
-      <c r="C60" s="32" t="s">
+      <c r="C60" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D60" s="32" t="s">
+      <c r="D60" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E60" s="32" t="s">
+      <c r="E60" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F60" s="32" t="s">
+      <c r="F60" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6006,27 +6070,27 @@
       <c r="B63" s="4" t="n">
         <v>2039</v>
       </c>
-      <c r="C63" s="32" t="n">
+      <c r="C63" s="29" t="n">
         <v>43</v>
       </c>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32" t="n">
+      <c r="D63" s="29"/>
+      <c r="E63" s="29" t="n">
         <v>44</v>
       </c>
-      <c r="F63" s="32"/>
+      <c r="F63" s="29"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4"/>
-      <c r="C64" s="32" t="s">
+      <c r="C64" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D64" s="32" t="s">
+      <c r="D64" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E64" s="32" t="s">
+      <c r="E64" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F64" s="32" t="s">
+      <c r="F64" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6060,27 +6124,27 @@
       <c r="B67" s="4" t="n">
         <v>2040</v>
       </c>
-      <c r="C67" s="32" t="n">
+      <c r="C67" s="29" t="n">
         <v>44</v>
       </c>
-      <c r="D67" s="32"/>
-      <c r="E67" s="32" t="n">
+      <c r="D67" s="29"/>
+      <c r="E67" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="F67" s="32"/>
+      <c r="F67" s="29"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4"/>
-      <c r="C68" s="32" t="s">
+      <c r="C68" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D68" s="32" t="s">
+      <c r="D68" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E68" s="32" t="s">
+      <c r="E68" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F68" s="32" t="s">
+      <c r="F68" s="29" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6116,27 +6180,27 @@
       <c r="B71" s="4" t="n">
         <v>2041</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C71" s="29" t="n">
         <v>45</v>
       </c>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32" t="n">
+      <c r="D71" s="29"/>
+      <c r="E71" s="29" t="n">
         <v>46</v>
       </c>
-      <c r="F71" s="32"/>
+      <c r="F71" s="29"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4"/>
-      <c r="C72" s="32" t="s">
+      <c r="C72" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="D72" s="32" t="s">
+      <c r="D72" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E72" s="32" t="s">
+      <c r="E72" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F72" s="32" t="s">
+      <c r="F72" s="29" t="s">
         <v>34</v>
       </c>
     </row>

--- a/Shedule/2025.xlsx
+++ b/Shedule/2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Plan" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="363">
   <si>
     <t xml:space="preserve">Daily Plan</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t xml:space="preserve">Shaft Software Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consultancy</t>
   </si>
   <si>
     <t xml:space="preserve">Milestone Software Technologies</t>
@@ -1281,7 +1284,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1378,23 +1381,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3241,8 +3240,12 @@
       <c r="D43" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
+      <c r="E43" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="21" t="n">
@@ -3254,8 +3257,12 @@
       <c r="D44" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
+      <c r="E44" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="21" t="n">
@@ -3267,93 +3274,121 @@
       <c r="D45" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
+      <c r="E45" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="21" t="n">
         <v>45</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
+      <c r="E46" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="21" t="n">
         <v>46</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D47" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
+      <c r="E47" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="21" t="n">
         <v>47</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D48" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
+      <c r="E48" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="21" t="n">
         <v>48</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D49" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
+      <c r="E49" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="21" t="n">
         <v>49</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D50" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
+      <c r="E50" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="21" t="n">
         <v>50</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D51" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
+      <c r="E51" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="21" t="n">
         <v>51</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D52" s="21" t="s">
         <v>74</v>
@@ -3366,7 +3401,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -3377,10 +3412,10 @@
         <v>53</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E54" s="21"/>
       <c r="F54" s="21"/>
@@ -3390,10 +3425,10 @@
         <v>54</v>
       </c>
       <c r="C55" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>125</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>124</v>
       </c>
       <c r="E55" s="21"/>
       <c r="F55" s="21"/>
@@ -3403,10 +3438,10 @@
         <v>55</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E56" s="21"/>
       <c r="F56" s="21"/>
@@ -3416,10 +3451,10 @@
         <v>56</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E57" s="21"/>
       <c r="F57" s="21"/>
@@ -3429,10 +3464,10 @@
         <v>57</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E58" s="21"/>
       <c r="F58" s="21"/>
@@ -3442,10 +3477,10 @@
         <v>58</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="21"/>
@@ -3455,10 +3490,10 @@
         <v>59</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="21"/>
@@ -3468,10 +3503,10 @@
         <v>60</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E61" s="21"/>
       <c r="F61" s="21"/>
@@ -3481,10 +3516,10 @@
         <v>61</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E62" s="21"/>
       <c r="F62" s="21"/>
@@ -3494,10 +3529,10 @@
         <v>62</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E63" s="21"/>
       <c r="F63" s="21"/>
@@ -3507,10 +3542,10 @@
         <v>63</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E64" s="21"/>
       <c r="F64" s="21"/>
@@ -3520,10 +3555,10 @@
         <v>64</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E65" s="21"/>
       <c r="F65" s="21"/>
@@ -3533,10 +3568,10 @@
         <v>65</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E66" s="21"/>
       <c r="F66" s="21"/>
@@ -3546,10 +3581,10 @@
         <v>66</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E67" s="21"/>
       <c r="F67" s="21"/>
@@ -3559,10 +3594,10 @@
         <v>67</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E68" s="21"/>
       <c r="F68" s="21"/>
@@ -3572,10 +3607,10 @@
         <v>68</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E69" s="21"/>
       <c r="F69" s="21"/>
@@ -3585,10 +3620,10 @@
         <v>69</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
@@ -3598,10 +3633,10 @@
         <v>70</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E71" s="21"/>
       <c r="F71" s="21"/>
@@ -3611,10 +3646,10 @@
         <v>71</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E72" s="21"/>
       <c r="F72" s="21"/>
@@ -3624,10 +3659,10 @@
         <v>72</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E73" s="21"/>
       <c r="F73" s="21"/>
@@ -3637,10 +3672,10 @@
         <v>73</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E74" s="21"/>
       <c r="F74" s="21"/>
@@ -3650,10 +3685,10 @@
         <v>74</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E75" s="21"/>
       <c r="F75" s="21"/>
@@ -3663,10 +3698,10 @@
         <v>75</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E76" s="21"/>
       <c r="F76" s="21"/>
@@ -3676,10 +3711,10 @@
         <v>76</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E77" s="21"/>
       <c r="F77" s="21"/>
@@ -3689,10 +3724,10 @@
         <v>77</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E78" s="21"/>
       <c r="F78" s="21"/>
@@ -3702,10 +3737,10 @@
         <v>78</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E79" s="23"/>
       <c r="F79" s="23"/>
@@ -3715,10 +3750,10 @@
         <v>79</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E80" s="23"/>
       <c r="F80" s="23"/>
@@ -3728,10 +3763,10 @@
         <v>80</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E81" s="23"/>
       <c r="F81" s="23"/>
@@ -3741,10 +3776,10 @@
         <v>81</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E82" s="23"/>
       <c r="F82" s="23"/>
@@ -3754,10 +3789,10 @@
         <v>82</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E83" s="23"/>
       <c r="F83" s="23"/>
@@ -3767,10 +3802,10 @@
         <v>83</v>
       </c>
       <c r="C84" s="22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E84" s="23"/>
       <c r="F84" s="23"/>
@@ -3780,10 +3815,10 @@
         <v>84</v>
       </c>
       <c r="C85" s="22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E85" s="23"/>
       <c r="F85" s="23"/>
@@ -3793,10 +3828,10 @@
         <v>85</v>
       </c>
       <c r="C86" s="22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E86" s="23"/>
       <c r="F86" s="23"/>
@@ -3806,10 +3841,10 @@
         <v>86</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E87" s="23"/>
       <c r="F87" s="23"/>
@@ -3819,10 +3854,10 @@
         <v>87</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E88" s="23"/>
       <c r="F88" s="23"/>
@@ -3832,10 +3867,10 @@
         <v>88</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E89" s="23"/>
       <c r="F89" s="23"/>
@@ -3845,10 +3880,10 @@
         <v>89</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E90" s="23"/>
       <c r="F90" s="23"/>
@@ -3858,10 +3893,10 @@
         <v>90</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E91" s="23"/>
       <c r="F91" s="23"/>
@@ -3871,10 +3906,10 @@
         <v>91</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E92" s="23"/>
       <c r="F92" s="23"/>
@@ -3884,10 +3919,10 @@
         <v>92</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D93" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E93" s="23"/>
       <c r="F93" s="23"/>
@@ -3897,10 +3932,10 @@
         <v>93</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E94" s="23"/>
       <c r="F94" s="23"/>
@@ -3910,10 +3945,10 @@
         <v>94</v>
       </c>
       <c r="C95" s="22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E95" s="23"/>
       <c r="F95" s="23"/>
@@ -3923,10 +3958,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E96" s="23"/>
       <c r="F96" s="23"/>
@@ -3936,10 +3971,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E97" s="23"/>
       <c r="F97" s="23"/>
@@ -3949,10 +3984,10 @@
         <v>97</v>
       </c>
       <c r="C98" s="22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
@@ -3962,10 +3997,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E99" s="23"/>
       <c r="F99" s="23"/>
@@ -3975,10 +4010,10 @@
         <v>99</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E100" s="23"/>
       <c r="F100" s="23"/>
@@ -3988,10 +4023,10 @@
         <v>100</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E101" s="23"/>
       <c r="F101" s="23"/>
@@ -4001,10 +4036,10 @@
         <v>101</v>
       </c>
       <c r="C102" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E102" s="23"/>
       <c r="F102" s="23"/>
@@ -4014,10 +4049,10 @@
         <v>102</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D103" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E103" s="23"/>
       <c r="F103" s="23"/>
@@ -4027,10 +4062,10 @@
         <v>103</v>
       </c>
       <c r="C104" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E104" s="23"/>
       <c r="F104" s="23"/>
@@ -4040,10 +4075,10 @@
         <v>104</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D105" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E105" s="23"/>
       <c r="F105" s="23"/>
@@ -4053,10 +4088,10 @@
         <v>105</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D106" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E106" s="23"/>
       <c r="F106" s="23"/>
@@ -4066,10 +4101,10 @@
         <v>106</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D107" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E107" s="23"/>
       <c r="F107" s="23"/>
@@ -4079,10 +4114,10 @@
         <v>107</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E108" s="23"/>
       <c r="F108" s="23"/>
@@ -4092,10 +4127,10 @@
         <v>108</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E109" s="23"/>
       <c r="F109" s="23"/>
@@ -4105,10 +4140,10 @@
         <v>109</v>
       </c>
       <c r="C110" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E110" s="23"/>
       <c r="F110" s="23"/>
@@ -4118,10 +4153,10 @@
         <v>110</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D111" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E111" s="23"/>
       <c r="F111" s="23"/>
@@ -4131,10 +4166,10 @@
         <v>111</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D112" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
@@ -4144,10 +4179,10 @@
         <v>112</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D113" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E113" s="23"/>
       <c r="F113" s="23"/>
@@ -4157,10 +4192,10 @@
         <v>113</v>
       </c>
       <c r="C114" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D114" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E114" s="23"/>
       <c r="F114" s="23"/>
@@ -4170,10 +4205,10 @@
         <v>114</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D115" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E115" s="23"/>
       <c r="F115" s="23"/>
@@ -4183,10 +4218,10 @@
         <v>115</v>
       </c>
       <c r="C116" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D116" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E116" s="23"/>
       <c r="F116" s="23"/>
@@ -4196,10 +4231,10 @@
         <v>116</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D117" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E117" s="23"/>
       <c r="F117" s="23"/>
@@ -4209,10 +4244,10 @@
         <v>117</v>
       </c>
       <c r="C118" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D118" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E118" s="23"/>
       <c r="F118" s="23"/>
@@ -4222,10 +4257,10 @@
         <v>118</v>
       </c>
       <c r="C119" s="22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D119" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E119" s="23"/>
       <c r="F119" s="23"/>
@@ -4235,10 +4270,10 @@
         <v>119</v>
       </c>
       <c r="C120" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E120" s="23"/>
       <c r="F120" s="23"/>
@@ -4248,10 +4283,10 @@
         <v>120</v>
       </c>
       <c r="C121" s="22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D121" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E121" s="23"/>
       <c r="F121" s="23"/>
@@ -4261,10 +4296,10 @@
         <v>121</v>
       </c>
       <c r="C122" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D122" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E122" s="23"/>
       <c r="F122" s="23"/>
@@ -4274,10 +4309,10 @@
         <v>122</v>
       </c>
       <c r="C123" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D123" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E123" s="23"/>
       <c r="F123" s="23"/>
@@ -4287,10 +4322,10 @@
         <v>123</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D124" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E124" s="23"/>
       <c r="F124" s="23"/>
@@ -4300,10 +4335,10 @@
         <v>124</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E125" s="23"/>
       <c r="F125" s="23"/>
@@ -4313,10 +4348,10 @@
         <v>125</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E126" s="23"/>
       <c r="F126" s="23"/>
@@ -4326,10 +4361,10 @@
         <v>126</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D127" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E127" s="23"/>
       <c r="F127" s="23"/>
@@ -4339,10 +4374,10 @@
         <v>127</v>
       </c>
       <c r="C128" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E128" s="23"/>
       <c r="F128" s="23"/>
@@ -4352,10 +4387,10 @@
         <v>128</v>
       </c>
       <c r="C129" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D129" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E129" s="23"/>
       <c r="F129" s="23"/>
@@ -4365,10 +4400,10 @@
         <v>129</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D130" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E130" s="23"/>
       <c r="F130" s="23"/>
@@ -4378,10 +4413,10 @@
         <v>130</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D131" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E131" s="23"/>
       <c r="F131" s="23"/>
@@ -4391,10 +4426,10 @@
         <v>131</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D132" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E132" s="23"/>
       <c r="F132" s="23"/>
@@ -4404,10 +4439,10 @@
         <v>132</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D133" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E133" s="23"/>
       <c r="F133" s="23"/>
@@ -4417,10 +4452,10 @@
         <v>133</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D134" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E134" s="23"/>
       <c r="F134" s="23"/>
@@ -4430,10 +4465,10 @@
         <v>134</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D135" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E135" s="23"/>
       <c r="F135" s="23"/>
@@ -4443,10 +4478,10 @@
         <v>135</v>
       </c>
       <c r="C136" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D136" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E136" s="23"/>
       <c r="F136" s="23"/>
@@ -4456,10 +4491,10 @@
         <v>136</v>
       </c>
       <c r="C137" s="22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D137" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E137" s="23"/>
       <c r="F137" s="23"/>
@@ -4469,10 +4504,10 @@
         <v>137</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D138" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E138" s="23"/>
       <c r="F138" s="23"/>
@@ -4482,10 +4517,10 @@
         <v>138</v>
       </c>
       <c r="C139" s="22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D139" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E139" s="23"/>
       <c r="F139" s="23"/>
@@ -4495,10 +4530,10 @@
         <v>139</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D140" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E140" s="23"/>
       <c r="F140" s="23"/>
@@ -4508,10 +4543,10 @@
         <v>140</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D141" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E141" s="23"/>
       <c r="F141" s="23"/>
@@ -4521,10 +4556,10 @@
         <v>141</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D142" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E142" s="23"/>
       <c r="F142" s="23"/>
@@ -4534,10 +4569,10 @@
         <v>142</v>
       </c>
       <c r="C143" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D143" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E143" s="23"/>
       <c r="F143" s="23"/>
@@ -4547,10 +4582,10 @@
         <v>143</v>
       </c>
       <c r="C144" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D144" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E144" s="23"/>
       <c r="F144" s="23"/>
@@ -4560,10 +4595,10 @@
         <v>144</v>
       </c>
       <c r="C145" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D145" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E145" s="23"/>
       <c r="F145" s="23"/>
@@ -4573,10 +4608,10 @@
         <v>145</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D146" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E146" s="23"/>
       <c r="F146" s="23"/>
@@ -4586,10 +4621,10 @@
         <v>146</v>
       </c>
       <c r="C147" s="22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D147" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E147" s="23"/>
       <c r="F147" s="23"/>
@@ -4599,10 +4634,10 @@
         <v>147</v>
       </c>
       <c r="C148" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D148" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E148" s="23"/>
       <c r="F148" s="23"/>
@@ -4612,10 +4647,10 @@
         <v>148</v>
       </c>
       <c r="C149" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E149" s="23"/>
       <c r="F149" s="23"/>
@@ -4625,10 +4660,10 @@
         <v>149</v>
       </c>
       <c r="C150" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D150" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E150" s="23"/>
       <c r="F150" s="23"/>
@@ -4638,10 +4673,10 @@
         <v>150</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D151" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E151" s="23"/>
       <c r="F151" s="23"/>
@@ -4651,10 +4686,10 @@
         <v>151</v>
       </c>
       <c r="C152" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D152" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E152" s="23"/>
       <c r="F152" s="23"/>
@@ -4664,10 +4699,10 @@
         <v>152</v>
       </c>
       <c r="C153" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D153" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E153" s="23"/>
       <c r="F153" s="23"/>
@@ -4677,10 +4712,10 @@
         <v>153</v>
       </c>
       <c r="C154" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D154" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E154" s="23"/>
       <c r="F154" s="23"/>
@@ -4690,10 +4725,10 @@
         <v>154</v>
       </c>
       <c r="C155" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D155" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E155" s="23"/>
       <c r="F155" s="23"/>
@@ -4703,10 +4738,10 @@
         <v>155</v>
       </c>
       <c r="C156" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D156" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E156" s="23"/>
       <c r="F156" s="23"/>
@@ -4716,10 +4751,10 @@
         <v>156</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D157" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E157" s="23"/>
       <c r="F157" s="23"/>
@@ -4729,10 +4764,10 @@
         <v>157</v>
       </c>
       <c r="C158" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D158" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E158" s="23"/>
       <c r="F158" s="23"/>
@@ -4742,10 +4777,10 @@
         <v>158</v>
       </c>
       <c r="C159" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D159" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E159" s="23"/>
       <c r="F159" s="23"/>
@@ -4755,10 +4790,10 @@
         <v>159</v>
       </c>
       <c r="C160" s="22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D160" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E160" s="23"/>
       <c r="F160" s="23"/>
@@ -4768,10 +4803,10 @@
         <v>160</v>
       </c>
       <c r="C161" s="22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D161" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E161" s="23"/>
       <c r="F161" s="23"/>
@@ -4781,10 +4816,10 @@
         <v>161</v>
       </c>
       <c r="C162" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D162" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E162" s="23"/>
       <c r="F162" s="23"/>
@@ -4794,10 +4829,10 @@
         <v>162</v>
       </c>
       <c r="C163" s="22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D163" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E163" s="23"/>
       <c r="F163" s="23"/>
@@ -5030,98 +5065,98 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="B3" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="E3" s="27" t="s">
+      <c r="C3" s="26" t="s">
         <v>245</v>
       </c>
+      <c r="D3" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>246</v>
+      </c>
       <c r="F3" s="26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="C4" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="B4" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="D4" s="26" t="s">
         <v>251</v>
       </c>
+      <c r="E4" s="26" t="s">
+        <v>252</v>
+      </c>
       <c r="F4" s="26" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="C5" s="27" t="s">
         <v>253</v>
       </c>
+      <c r="B5" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>254</v>
+      </c>
       <c r="D5" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="E5" s="27" t="s">
         <v>255</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>256</v>
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="B6" s="27" t="s">
         <v>257</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>258</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -5131,8 +5166,8 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26"/>
-      <c r="B7" s="27" t="s">
-        <v>258</v>
+      <c r="B7" s="26" t="s">
+        <v>259</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
@@ -5141,7 +5176,7 @@
       <c r="G7" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="28"/>
+      <c r="D11" s="27"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5170,7 +5205,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -5180,7 +5215,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>34</v>
@@ -5190,8 +5225,8 @@
       <c r="B4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>261</v>
+      <c r="C4" s="28" t="s">
+        <v>262</v>
       </c>
       <c r="D4" s="15"/>
     </row>
@@ -5199,8 +5234,8 @@
       <c r="B5" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="29" t="s">
-        <v>262</v>
+      <c r="C5" s="28" t="s">
+        <v>263</v>
       </c>
       <c r="D5" s="15"/>
     </row>
@@ -5208,8 +5243,8 @@
       <c r="B6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>263</v>
+      <c r="C6" s="28" t="s">
+        <v>264</v>
       </c>
       <c r="D6" s="15"/>
     </row>
@@ -5217,8 +5252,8 @@
       <c r="B7" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="29" t="s">
-        <v>264</v>
+      <c r="C7" s="28" t="s">
+        <v>265</v>
       </c>
       <c r="D7" s="15"/>
     </row>
@@ -5226,8 +5261,8 @@
       <c r="B8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="29" t="s">
-        <v>265</v>
+      <c r="C8" s="28" t="s">
+        <v>266</v>
       </c>
       <c r="D8" s="15"/>
     </row>
@@ -5235,28 +5270,28 @@
       <c r="B9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="29"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="29"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="29"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="29"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="15"/>
     </row>
   </sheetData>
@@ -5281,488 +5316,488 @@
   <dimension ref="B2:F35"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="37.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="32"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="30" width="9.14"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="29" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="29" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="29" width="37.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="29" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="29" width="25.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="29" width="32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="29" width="9.14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="31" t="n">
+      <c r="B3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="E3" s="32" t="s">
+      <c r="C3" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="E3" s="31" t="s">
         <v>273</v>
       </c>
+      <c r="F3" s="31" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="31" t="n">
+      <c r="B4" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="D4" s="31" t="s">
+      <c r="C4" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="D4" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="E4" s="31" t="s">
         <v>277</v>
       </c>
+      <c r="F4" s="31" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="D5" s="31" t="s">
+      <c r="C5" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="D5" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="E5" s="31" t="s">
         <v>281</v>
       </c>
+      <c r="F5" s="31" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="31" t="s">
+      <c r="C6" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="D6" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="E6" s="31" t="s">
         <v>285</v>
       </c>
+      <c r="F6" s="31" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="D7" s="31" t="s">
+      <c r="C7" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="D7" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="E7" s="31" t="s">
         <v>289</v>
       </c>
+      <c r="F7" s="31" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>290</v>
-      </c>
-      <c r="D8" s="31" t="s">
+      <c r="C8" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="D8" s="30" t="s">
         <v>292</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="E8" s="31" t="s">
         <v>293</v>
       </c>
+      <c r="F8" s="31" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="D9" s="31" t="s">
+      <c r="C9" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="D9" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="E9" s="31" t="s">
         <v>297</v>
       </c>
+      <c r="F9" s="31" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>298</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="E10" s="32" t="s">
+      <c r="C10" s="31" t="s">
         <v>299</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="D10" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="E10" s="31" t="s">
         <v>300</v>
       </c>
+      <c r="F10" s="31" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="32" t="s">
-        <v>301</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="E11" s="32" t="s">
+      <c r="C11" s="31" t="s">
         <v>302</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="D11" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="E11" s="31" t="s">
         <v>303</v>
       </c>
+      <c r="F11" s="31" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>279</v>
-      </c>
-      <c r="E12" s="32" t="s">
+      <c r="C12" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="D12" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="E12" s="31" t="s">
         <v>306</v>
       </c>
+      <c r="F12" s="31" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="E13" s="32" t="s">
+      <c r="C13" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="D13" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="E13" s="31" t="s">
         <v>309</v>
       </c>
+      <c r="F13" s="31" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="E14" s="32" t="s">
+      <c r="C14" s="31" t="s">
         <v>311</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="D14" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="E14" s="31" t="s">
         <v>312</v>
       </c>
+      <c r="F14" s="31" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="E15" s="32" t="s">
+      <c r="C15" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="D15" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="E15" s="31" t="s">
         <v>315</v>
       </c>
+      <c r="F15" s="31" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="31" t="n">
+      <c r="B16" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="E16" s="32" t="s">
+      <c r="C16" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="D16" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="E16" s="31" t="s">
         <v>318</v>
       </c>
+      <c r="F16" s="31" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>279</v>
-      </c>
-      <c r="E17" s="32" t="s">
+      <c r="C17" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="D17" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="E17" s="31" t="s">
         <v>321</v>
       </c>
+      <c r="F17" s="31" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="31" t="n">
+      <c r="B18" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="32" t="s">
-        <v>322</v>
-      </c>
-      <c r="D18" s="31" t="s">
+      <c r="C18" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="D18" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="E18" s="31" t="s">
         <v>325</v>
       </c>
+      <c r="F18" s="31" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="31" t="n">
+      <c r="B19" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="D19" s="31" t="s">
+      <c r="C19" s="31" t="s">
         <v>327</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="D19" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="E19" s="31" t="s">
         <v>329</v>
       </c>
+      <c r="F19" s="31" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="32" t="s">
-        <v>330</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="E20" s="32" t="s">
+      <c r="C20" s="31" t="s">
         <v>331</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="D20" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="E20" s="31" t="s">
         <v>332</v>
       </c>
+      <c r="F20" s="31" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="32" t="s">
-        <v>333</v>
-      </c>
-      <c r="D21" s="31" t="s">
+      <c r="C21" s="31" t="s">
         <v>334</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="D21" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="F21" s="32" t="s">
+      <c r="E21" s="31" t="s">
         <v>336</v>
       </c>
+      <c r="F21" s="31" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="32" t="s">
-        <v>337</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>323</v>
-      </c>
-      <c r="E22" s="32" t="s">
+      <c r="C22" s="31" t="s">
         <v>338</v>
       </c>
-      <c r="F22" s="32" t="s">
+      <c r="D22" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="E22" s="31" t="s">
         <v>339</v>
       </c>
+      <c r="F22" s="31" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="31" t="n">
+      <c r="B28" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="31" t="n">
+      <c r="B29" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="31" t="n">
+      <c r="B30" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="32"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="31" t="n">
+      <c r="B31" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="31" t="n">
+      <c r="B32" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="30" t="n">
         <v>32</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="C35" s="32"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5793,55 +5828,55 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="33" t="s">
-        <v>340</v>
-      </c>
-      <c r="C2" s="33" t="s">
+      <c r="B2" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C3" s="33" t="n">
+      <c r="C3" s="32" t="n">
         <v>29</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33" t="n">
+      <c r="D3" s="32"/>
+      <c r="E3" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="33"/>
+      <c r="F3" s="32"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4"/>
-      <c r="C4" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D4" s="33" t="s">
+      <c r="C4" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F4" s="33" t="s">
+      <c r="E4" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F4" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4"/>
       <c r="C5" s="21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D5" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F5" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -5851,14 +5886,14 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4"/>
       <c r="C6" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D6" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F6" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -5868,16 +5903,16 @@
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4"/>
       <c r="C7" s="21" t="s">
-        <v>347</v>
-      </c>
-      <c r="D7" s="34" t="b">
+        <v>348</v>
+      </c>
+      <c r="D7" s="33" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="F7" s="34" t="b">
+        <v>346</v>
+      </c>
+      <c r="F7" s="33" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -5885,16 +5920,16 @@
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4"/>
       <c r="C8" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="D8" s="33" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>348</v>
       </c>
-      <c r="D8" s="34" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>347</v>
-      </c>
-      <c r="F8" s="34" t="b">
+      <c r="F8" s="33" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -5903,41 +5938,41 @@
       <c r="B9" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33" t="n">
+      <c r="D9" s="32"/>
+      <c r="E9" s="32" t="n">
         <v>31</v>
       </c>
-      <c r="F9" s="33"/>
+      <c r="F9" s="32"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4"/>
-      <c r="C10" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D10" s="33" t="s">
+      <c r="C10" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F10" s="33" t="s">
+      <c r="E10" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F10" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4"/>
       <c r="C11" s="21" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D11" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F11" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -5947,14 +5982,14 @@
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4"/>
       <c r="C12" s="21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D12" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F12" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -5964,16 +5999,16 @@
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4"/>
       <c r="C13" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="D13" s="34" t="b">
+        <v>346</v>
+      </c>
+      <c r="D13" s="33" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="F13" s="34" t="b">
+        <v>352</v>
+      </c>
+      <c r="F13" s="33" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -5982,41 +6017,41 @@
       <c r="B14" s="4" t="n">
         <v>2027</v>
       </c>
-      <c r="C14" s="33" t="n">
+      <c r="C14" s="32" t="n">
         <v>31</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33" t="n">
+      <c r="D14" s="32"/>
+      <c r="E14" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="F14" s="33"/>
+      <c r="F14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4"/>
-      <c r="C15" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D15" s="33" t="s">
+      <c r="C15" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D15" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F15" s="33" t="s">
+      <c r="E15" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F15" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4"/>
       <c r="C16" s="21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D16" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F16" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6026,7 +6061,7 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4"/>
       <c r="C17" s="21" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D17" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6042,34 +6077,34 @@
       <c r="B18" s="4" t="n">
         <v>2028</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="34" t="n">
         <v>32</v>
       </c>
-      <c r="D18" s="35"/>
-      <c r="E18" s="33" t="n">
+      <c r="D18" s="34"/>
+      <c r="E18" s="32" t="n">
         <v>33</v>
       </c>
-      <c r="F18" s="33"/>
+      <c r="F18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4"/>
-      <c r="C19" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="D19" s="33" t="s">
+      <c r="C19" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="D19" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F19" s="33" t="s">
+      <c r="E19" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F19" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="4"/>
-      <c r="C20" s="36" t="s">
-        <v>356</v>
+      <c r="C20" s="35" t="s">
+        <v>357</v>
       </c>
       <c r="D20" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6083,8 +6118,8 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="4"/>
-      <c r="C21" s="36" t="s">
-        <v>357</v>
+      <c r="C21" s="35" t="s">
+        <v>358</v>
       </c>
       <c r="D21" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6099,7 +6134,7 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4"/>
       <c r="C22" s="21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D22" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6115,27 +6150,27 @@
       <c r="B23" s="4" t="n">
         <v>2029</v>
       </c>
-      <c r="C23" s="33" t="n">
+      <c r="C23" s="32" t="n">
         <v>33</v>
       </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33" t="n">
+      <c r="D23" s="32"/>
+      <c r="E23" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="F23" s="33"/>
+      <c r="F23" s="32"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4"/>
-      <c r="C24" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D24" s="33" t="s">
+      <c r="C24" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F24" s="33" t="s">
+      <c r="E24" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F24" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6169,27 +6204,27 @@
       <c r="B27" s="4" t="n">
         <v>2030</v>
       </c>
-      <c r="C27" s="33" t="n">
+      <c r="C27" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33" t="n">
+      <c r="D27" s="32"/>
+      <c r="E27" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="F27" s="33"/>
+      <c r="F27" s="32"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4"/>
-      <c r="C28" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D28" s="33" t="s">
+      <c r="C28" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D28" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F28" s="33" t="s">
+      <c r="E28" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F28" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6201,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F29" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6225,34 +6260,34 @@
       <c r="B31" s="4" t="n">
         <v>2031</v>
       </c>
-      <c r="C31" s="33" t="n">
+      <c r="C31" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33" t="n">
+      <c r="D31" s="32"/>
+      <c r="E31" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="F31" s="33"/>
+      <c r="F31" s="32"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4"/>
-      <c r="C32" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D32" s="33" t="s">
+      <c r="C32" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D32" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F32" s="33" t="s">
+      <c r="E32" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F32" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4"/>
       <c r="C33" s="21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D33" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6281,27 +6316,27 @@
       <c r="B35" s="4" t="n">
         <v>2032</v>
       </c>
-      <c r="C35" s="33" t="n">
+      <c r="C35" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33" t="n">
+      <c r="D35" s="32"/>
+      <c r="E35" s="32" t="n">
         <v>37</v>
       </c>
-      <c r="F35" s="33"/>
+      <c r="F35" s="32"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4"/>
-      <c r="C36" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D36" s="33" t="s">
+      <c r="C36" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F36" s="33" t="s">
+      <c r="E36" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F36" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6335,27 +6370,27 @@
       <c r="B39" s="4" t="n">
         <v>2033</v>
       </c>
-      <c r="C39" s="33" t="n">
+      <c r="C39" s="32" t="n">
         <v>37</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33" t="n">
+      <c r="D39" s="32"/>
+      <c r="E39" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="F39" s="33"/>
+      <c r="F39" s="32"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4"/>
-      <c r="C40" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D40" s="33" t="s">
+      <c r="C40" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D40" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F40" s="33" t="s">
+      <c r="E40" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F40" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6389,27 +6424,27 @@
       <c r="B43" s="4" t="n">
         <v>2034</v>
       </c>
-      <c r="C43" s="33" t="n">
+      <c r="C43" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33" t="n">
+      <c r="D43" s="32"/>
+      <c r="E43" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="F43" s="33"/>
+      <c r="F43" s="32"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4"/>
-      <c r="C44" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D44" s="33" t="s">
+      <c r="C44" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D44" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F44" s="33" t="s">
+      <c r="E44" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F44" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6443,27 +6478,27 @@
       <c r="B47" s="4" t="n">
         <v>2035</v>
       </c>
-      <c r="C47" s="33" t="n">
+      <c r="C47" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33" t="n">
+      <c r="D47" s="32"/>
+      <c r="E47" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="F47" s="33"/>
+      <c r="F47" s="32"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4"/>
-      <c r="C48" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D48" s="33" t="s">
+      <c r="C48" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D48" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E48" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F48" s="33" t="s">
+      <c r="E48" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F48" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6475,7 +6510,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F49" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6499,34 +6534,34 @@
       <c r="B51" s="4" t="n">
         <v>2036</v>
       </c>
-      <c r="C51" s="33" t="n">
+      <c r="C51" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33" t="n">
+      <c r="D51" s="32"/>
+      <c r="E51" s="32" t="n">
         <v>41</v>
       </c>
-      <c r="F51" s="33"/>
+      <c r="F51" s="32"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4"/>
-      <c r="C52" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D52" s="33" t="s">
+      <c r="C52" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D52" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E52" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F52" s="33" t="s">
+      <c r="E52" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F52" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="4"/>
       <c r="C53" s="21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D53" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6555,27 +6590,27 @@
       <c r="B55" s="4" t="n">
         <v>2037</v>
       </c>
-      <c r="C55" s="33" t="n">
+      <c r="C55" s="32" t="n">
         <v>41</v>
       </c>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33" t="n">
+      <c r="D55" s="32"/>
+      <c r="E55" s="32" t="n">
         <v>42</v>
       </c>
-      <c r="F55" s="33"/>
+      <c r="F55" s="32"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="4"/>
-      <c r="C56" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D56" s="33" t="s">
+      <c r="C56" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D56" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E56" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F56" s="33" t="s">
+      <c r="E56" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F56" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6609,27 +6644,27 @@
       <c r="B59" s="4" t="n">
         <v>2038</v>
       </c>
-      <c r="C59" s="33" t="n">
+      <c r="C59" s="32" t="n">
         <v>42</v>
       </c>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33" t="n">
+      <c r="D59" s="32"/>
+      <c r="E59" s="32" t="n">
         <v>43</v>
       </c>
-      <c r="F59" s="33"/>
+      <c r="F59" s="32"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4"/>
-      <c r="C60" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D60" s="33" t="s">
+      <c r="C60" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D60" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E60" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F60" s="33" t="s">
+      <c r="E60" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F60" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6663,27 +6698,27 @@
       <c r="B63" s="4" t="n">
         <v>2039</v>
       </c>
-      <c r="C63" s="33" t="n">
+      <c r="C63" s="32" t="n">
         <v>43</v>
       </c>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="F63" s="33"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="F63" s="32"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4"/>
-      <c r="C64" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D64" s="33" t="s">
+      <c r="C64" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D64" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E64" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F64" s="33" t="s">
+      <c r="E64" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F64" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6717,27 +6752,27 @@
       <c r="B67" s="4" t="n">
         <v>2040</v>
       </c>
-      <c r="C67" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33" t="n">
+      <c r="C67" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="F67" s="33"/>
+      <c r="F67" s="32"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4"/>
-      <c r="C68" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D68" s="33" t="s">
+      <c r="C68" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D68" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E68" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F68" s="33" t="s">
+      <c r="E68" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F68" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6749,7 +6784,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F69" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6773,34 +6808,34 @@
       <c r="B71" s="4" t="n">
         <v>2041</v>
       </c>
-      <c r="C71" s="33" t="n">
+      <c r="C71" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33" t="n">
+      <c r="D71" s="32"/>
+      <c r="E71" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="F71" s="33"/>
+      <c r="F71" s="32"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4"/>
-      <c r="C72" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="D72" s="33" t="s">
+      <c r="C72" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D72" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E72" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="F72" s="33" t="s">
+      <c r="E72" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="F72" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4"/>
       <c r="C73" s="21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D73" s="23" t="b">
         <f aca="false">FALSE()</f>

--- a/Shedule/2025.xlsx
+++ b/Shedule/2025.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="368">
   <si>
     <t xml:space="preserve">Daily Plan</t>
   </si>
@@ -398,6 +398,9 @@
     <t xml:space="preserve">Logic Information Systems (INDIA) Pvt Ltd</t>
   </si>
   <si>
+    <t xml:space="preserve">only prefered experience</t>
+  </si>
+  <si>
     <t xml:space="preserve">Techknowspro Software and Hardware Development Company</t>
   </si>
   <si>
@@ -735,6 +738,18 @@
   </si>
   <si>
     <t xml:space="preserve">Dataroots Technologies LLP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-11-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Find</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending</t>
   </si>
   <si>
     <t xml:space="preserve">Indeed</t>
@@ -1126,7 +1141,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="hh:mm:ss"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1227,6 +1242,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1284,7 +1305,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1378,6 +1399,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3393,120 +3418,154 @@
       <c r="D52" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
+      <c r="E52" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="21" t="n">
         <v>52</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
+      <c r="F53" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="21" t="n">
         <v>53</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
+        <v>126</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="21" t="n">
         <v>54</v>
       </c>
       <c r="C55" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="D55" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
+      <c r="E55" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="21" t="n">
         <v>55</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
+        <v>126</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="21" t="n">
         <v>56</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
+        <v>126</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="21" t="n">
         <v>57</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
+        <v>126</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="21" t="n">
         <v>58</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
+        <v>126</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="21" t="n">
         <v>59</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
+        <v>126</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="21" t="n">
         <v>60</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E61" s="21"/>
       <c r="F61" s="21"/>
@@ -3516,10 +3575,10 @@
         <v>61</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E62" s="21"/>
       <c r="F62" s="21"/>
@@ -3529,10 +3588,10 @@
         <v>62</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E63" s="21"/>
       <c r="F63" s="21"/>
@@ -3542,10 +3601,10 @@
         <v>63</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E64" s="21"/>
       <c r="F64" s="21"/>
@@ -3555,10 +3614,10 @@
         <v>64</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E65" s="21"/>
       <c r="F65" s="21"/>
@@ -3568,10 +3627,10 @@
         <v>65</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E66" s="21"/>
       <c r="F66" s="21"/>
@@ -3581,10 +3640,10 @@
         <v>66</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E67" s="21"/>
       <c r="F67" s="21"/>
@@ -3594,10 +3653,10 @@
         <v>67</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E68" s="21"/>
       <c r="F68" s="21"/>
@@ -3607,10 +3666,10 @@
         <v>68</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E69" s="21"/>
       <c r="F69" s="21"/>
@@ -3620,10 +3679,10 @@
         <v>69</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
@@ -3633,10 +3692,10 @@
         <v>70</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E71" s="21"/>
       <c r="F71" s="21"/>
@@ -3646,10 +3705,10 @@
         <v>71</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E72" s="21"/>
       <c r="F72" s="21"/>
@@ -3659,10 +3718,10 @@
         <v>72</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E73" s="21"/>
       <c r="F73" s="21"/>
@@ -3672,10 +3731,10 @@
         <v>73</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E74" s="21"/>
       <c r="F74" s="21"/>
@@ -3685,10 +3744,10 @@
         <v>74</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E75" s="21"/>
       <c r="F75" s="21"/>
@@ -3698,10 +3757,10 @@
         <v>75</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E76" s="21"/>
       <c r="F76" s="21"/>
@@ -3711,10 +3770,10 @@
         <v>76</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E77" s="21"/>
       <c r="F77" s="21"/>
@@ -3724,10 +3783,10 @@
         <v>77</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E78" s="21"/>
       <c r="F78" s="21"/>
@@ -3737,10 +3796,10 @@
         <v>78</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E79" s="23"/>
       <c r="F79" s="23"/>
@@ -3750,10 +3809,10 @@
         <v>79</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E80" s="23"/>
       <c r="F80" s="23"/>
@@ -3763,10 +3822,10 @@
         <v>80</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E81" s="23"/>
       <c r="F81" s="23"/>
@@ -3776,10 +3835,10 @@
         <v>81</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E82" s="23"/>
       <c r="F82" s="23"/>
@@ -3789,10 +3848,10 @@
         <v>82</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E83" s="23"/>
       <c r="F83" s="23"/>
@@ -3802,10 +3861,10 @@
         <v>83</v>
       </c>
       <c r="C84" s="22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E84" s="23"/>
       <c r="F84" s="23"/>
@@ -3815,10 +3874,10 @@
         <v>84</v>
       </c>
       <c r="C85" s="22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E85" s="23"/>
       <c r="F85" s="23"/>
@@ -3828,10 +3887,10 @@
         <v>85</v>
       </c>
       <c r="C86" s="22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E86" s="23"/>
       <c r="F86" s="23"/>
@@ -3841,10 +3900,10 @@
         <v>86</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E87" s="23"/>
       <c r="F87" s="23"/>
@@ -3854,10 +3913,10 @@
         <v>87</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E88" s="23"/>
       <c r="F88" s="23"/>
@@ -3867,10 +3926,10 @@
         <v>88</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E89" s="23"/>
       <c r="F89" s="23"/>
@@ -3880,10 +3939,10 @@
         <v>89</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E90" s="23"/>
       <c r="F90" s="23"/>
@@ -3893,10 +3952,10 @@
         <v>90</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E91" s="23"/>
       <c r="F91" s="23"/>
@@ -3906,10 +3965,10 @@
         <v>91</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E92" s="23"/>
       <c r="F92" s="23"/>
@@ -3919,10 +3978,10 @@
         <v>92</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D93" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E93" s="23"/>
       <c r="F93" s="23"/>
@@ -3932,10 +3991,10 @@
         <v>93</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E94" s="23"/>
       <c r="F94" s="23"/>
@@ -3945,10 +4004,10 @@
         <v>94</v>
       </c>
       <c r="C95" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E95" s="23"/>
       <c r="F95" s="23"/>
@@ -3958,10 +4017,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E96" s="23"/>
       <c r="F96" s="23"/>
@@ -3971,10 +4030,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E97" s="23"/>
       <c r="F97" s="23"/>
@@ -3984,10 +4043,10 @@
         <v>97</v>
       </c>
       <c r="C98" s="22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E98" s="23"/>
       <c r="F98" s="23"/>
@@ -3997,10 +4056,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E99" s="23"/>
       <c r="F99" s="23"/>
@@ -4010,10 +4069,10 @@
         <v>99</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E100" s="23"/>
       <c r="F100" s="23"/>
@@ -4023,10 +4082,10 @@
         <v>100</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E101" s="23"/>
       <c r="F101" s="23"/>
@@ -4036,10 +4095,10 @@
         <v>101</v>
       </c>
       <c r="C102" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E102" s="23"/>
       <c r="F102" s="23"/>
@@ -4049,10 +4108,10 @@
         <v>102</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D103" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E103" s="23"/>
       <c r="F103" s="23"/>
@@ -4062,10 +4121,10 @@
         <v>103</v>
       </c>
       <c r="C104" s="22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E104" s="23"/>
       <c r="F104" s="23"/>
@@ -4075,10 +4134,10 @@
         <v>104</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D105" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E105" s="23"/>
       <c r="F105" s="23"/>
@@ -4088,10 +4147,10 @@
         <v>105</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D106" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E106" s="23"/>
       <c r="F106" s="23"/>
@@ -4101,10 +4160,10 @@
         <v>106</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D107" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E107" s="23"/>
       <c r="F107" s="23"/>
@@ -4114,10 +4173,10 @@
         <v>107</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E108" s="23"/>
       <c r="F108" s="23"/>
@@ -4127,10 +4186,10 @@
         <v>108</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E109" s="23"/>
       <c r="F109" s="23"/>
@@ -4140,10 +4199,10 @@
         <v>109</v>
       </c>
       <c r="C110" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E110" s="23"/>
       <c r="F110" s="23"/>
@@ -4153,10 +4212,10 @@
         <v>110</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D111" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E111" s="23"/>
       <c r="F111" s="23"/>
@@ -4166,10 +4225,10 @@
         <v>111</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D112" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E112" s="23"/>
       <c r="F112" s="23"/>
@@ -4179,10 +4238,10 @@
         <v>112</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D113" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E113" s="23"/>
       <c r="F113" s="23"/>
@@ -4192,10 +4251,10 @@
         <v>113</v>
       </c>
       <c r="C114" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D114" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E114" s="23"/>
       <c r="F114" s="23"/>
@@ -4205,10 +4264,10 @@
         <v>114</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D115" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E115" s="23"/>
       <c r="F115" s="23"/>
@@ -4218,10 +4277,10 @@
         <v>115</v>
       </c>
       <c r="C116" s="22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D116" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E116" s="23"/>
       <c r="F116" s="23"/>
@@ -4231,10 +4290,10 @@
         <v>116</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D117" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E117" s="23"/>
       <c r="F117" s="23"/>
@@ -4244,10 +4303,10 @@
         <v>117</v>
       </c>
       <c r="C118" s="22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D118" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E118" s="23"/>
       <c r="F118" s="23"/>
@@ -4257,10 +4316,10 @@
         <v>118</v>
       </c>
       <c r="C119" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D119" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E119" s="23"/>
       <c r="F119" s="23"/>
@@ -4270,10 +4329,10 @@
         <v>119</v>
       </c>
       <c r="C120" s="22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E120" s="23"/>
       <c r="F120" s="23"/>
@@ -4283,10 +4342,10 @@
         <v>120</v>
       </c>
       <c r="C121" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D121" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E121" s="23"/>
       <c r="F121" s="23"/>
@@ -4296,10 +4355,10 @@
         <v>121</v>
       </c>
       <c r="C122" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D122" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E122" s="23"/>
       <c r="F122" s="23"/>
@@ -4309,10 +4368,10 @@
         <v>122</v>
       </c>
       <c r="C123" s="22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D123" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E123" s="23"/>
       <c r="F123" s="23"/>
@@ -4322,10 +4381,10 @@
         <v>123</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D124" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E124" s="23"/>
       <c r="F124" s="23"/>
@@ -4335,10 +4394,10 @@
         <v>124</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E125" s="23"/>
       <c r="F125" s="23"/>
@@ -4348,10 +4407,10 @@
         <v>125</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E126" s="23"/>
       <c r="F126" s="23"/>
@@ -4361,10 +4420,10 @@
         <v>126</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D127" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E127" s="23"/>
       <c r="F127" s="23"/>
@@ -4374,10 +4433,10 @@
         <v>127</v>
       </c>
       <c r="C128" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E128" s="23"/>
       <c r="F128" s="23"/>
@@ -4387,10 +4446,10 @@
         <v>128</v>
       </c>
       <c r="C129" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D129" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E129" s="23"/>
       <c r="F129" s="23"/>
@@ -4400,10 +4459,10 @@
         <v>129</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D130" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E130" s="23"/>
       <c r="F130" s="23"/>
@@ -4413,10 +4472,10 @@
         <v>130</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D131" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E131" s="23"/>
       <c r="F131" s="23"/>
@@ -4426,10 +4485,10 @@
         <v>131</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D132" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E132" s="23"/>
       <c r="F132" s="23"/>
@@ -4439,10 +4498,10 @@
         <v>132</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D133" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E133" s="23"/>
       <c r="F133" s="23"/>
@@ -4452,10 +4511,10 @@
         <v>133</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D134" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E134" s="23"/>
       <c r="F134" s="23"/>
@@ -4465,10 +4524,10 @@
         <v>134</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D135" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E135" s="23"/>
       <c r="F135" s="23"/>
@@ -4478,10 +4537,10 @@
         <v>135</v>
       </c>
       <c r="C136" s="22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D136" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E136" s="23"/>
       <c r="F136" s="23"/>
@@ -4491,10 +4550,10 @@
         <v>136</v>
       </c>
       <c r="C137" s="22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D137" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E137" s="23"/>
       <c r="F137" s="23"/>
@@ -4504,10 +4563,10 @@
         <v>137</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D138" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E138" s="23"/>
       <c r="F138" s="23"/>
@@ -4517,10 +4576,10 @@
         <v>138</v>
       </c>
       <c r="C139" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D139" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E139" s="23"/>
       <c r="F139" s="23"/>
@@ -4530,10 +4589,10 @@
         <v>139</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D140" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E140" s="23"/>
       <c r="F140" s="23"/>
@@ -4543,10 +4602,10 @@
         <v>140</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D141" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E141" s="23"/>
       <c r="F141" s="23"/>
@@ -4556,10 +4615,10 @@
         <v>141</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D142" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E142" s="23"/>
       <c r="F142" s="23"/>
@@ -4569,10 +4628,10 @@
         <v>142</v>
       </c>
       <c r="C143" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D143" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E143" s="23"/>
       <c r="F143" s="23"/>
@@ -4582,10 +4641,10 @@
         <v>143</v>
       </c>
       <c r="C144" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D144" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E144" s="23"/>
       <c r="F144" s="23"/>
@@ -4595,10 +4654,10 @@
         <v>144</v>
       </c>
       <c r="C145" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D145" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E145" s="23"/>
       <c r="F145" s="23"/>
@@ -4608,10 +4667,10 @@
         <v>145</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D146" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E146" s="23"/>
       <c r="F146" s="23"/>
@@ -4621,10 +4680,10 @@
         <v>146</v>
       </c>
       <c r="C147" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D147" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E147" s="23"/>
       <c r="F147" s="23"/>
@@ -4634,10 +4693,10 @@
         <v>147</v>
       </c>
       <c r="C148" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D148" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E148" s="23"/>
       <c r="F148" s="23"/>
@@ -4647,10 +4706,10 @@
         <v>148</v>
       </c>
       <c r="C149" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E149" s="23"/>
       <c r="F149" s="23"/>
@@ -4660,10 +4719,10 @@
         <v>149</v>
       </c>
       <c r="C150" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D150" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E150" s="23"/>
       <c r="F150" s="23"/>
@@ -4673,10 +4732,10 @@
         <v>150</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D151" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E151" s="23"/>
       <c r="F151" s="23"/>
@@ -4686,10 +4745,10 @@
         <v>151</v>
       </c>
       <c r="C152" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D152" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E152" s="23"/>
       <c r="F152" s="23"/>
@@ -4699,10 +4758,10 @@
         <v>152</v>
       </c>
       <c r="C153" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D153" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E153" s="23"/>
       <c r="F153" s="23"/>
@@ -4712,10 +4771,10 @@
         <v>153</v>
       </c>
       <c r="C154" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D154" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E154" s="23"/>
       <c r="F154" s="23"/>
@@ -4725,10 +4784,10 @@
         <v>154</v>
       </c>
       <c r="C155" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D155" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E155" s="23"/>
       <c r="F155" s="23"/>
@@ -4738,10 +4797,10 @@
         <v>155</v>
       </c>
       <c r="C156" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D156" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E156" s="23"/>
       <c r="F156" s="23"/>
@@ -4751,10 +4810,10 @@
         <v>156</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D157" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E157" s="23"/>
       <c r="F157" s="23"/>
@@ -4764,10 +4823,10 @@
         <v>157</v>
       </c>
       <c r="C158" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D158" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E158" s="23"/>
       <c r="F158" s="23"/>
@@ -4777,10 +4836,10 @@
         <v>158</v>
       </c>
       <c r="C159" s="22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D159" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E159" s="23"/>
       <c r="F159" s="23"/>
@@ -4790,10 +4849,10 @@
         <v>159</v>
       </c>
       <c r="C160" s="22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D160" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E160" s="23"/>
       <c r="F160" s="23"/>
@@ -4803,10 +4862,10 @@
         <v>160</v>
       </c>
       <c r="C161" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D161" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E161" s="23"/>
       <c r="F161" s="23"/>
@@ -4816,10 +4875,10 @@
         <v>161</v>
       </c>
       <c r="C162" s="22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D162" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E162" s="23"/>
       <c r="F162" s="23"/>
@@ -4829,10 +4888,10 @@
         <v>162</v>
       </c>
       <c r="C163" s="22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D163" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E163" s="23"/>
       <c r="F163" s="23"/>
@@ -4853,7 +4912,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G17"/>
+  <dimension ref="B2:H17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="11.53"/>
@@ -4873,12 +4932,15 @@
         <v>60</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4887,12 +4949,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+        <v>238</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" s="24" t="n">
+        <v>9600082498</v>
+      </c>
       <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="G3" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="H3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="n">
@@ -4903,6 +4972,7 @@
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="15" t="n">
@@ -4913,6 +4983,7 @@
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="15" t="n">
@@ -4923,6 +4994,7 @@
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="15" t="n">
@@ -4933,6 +5005,7 @@
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="15" t="n">
@@ -4943,6 +5016,7 @@
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="15" t="n">
@@ -4953,6 +5027,7 @@
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="15" t="n">
@@ -4963,6 +5038,7 @@
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="15" t="n">
@@ -4973,6 +5049,7 @@
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="15" t="n">
@@ -4983,6 +5060,7 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="15" t="n">
@@ -4993,6 +5071,7 @@
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="15" t="n">
@@ -5003,6 +5082,7 @@
       <c r="E14" s="15"/>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="15" t="n">
@@ -5013,6 +5093,7 @@
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="15" t="n">
@@ -5023,6 +5104,7 @@
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="15" t="n">
@@ -5033,6 +5115,7 @@
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5053,130 +5136,130 @@
   <dimension ref="A2:G11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="24" width="25.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="24" width="24.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="24" width="27.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="24" width="30.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="24" width="27.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="24" width="23.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="24" width="24.8"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="24" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="25" width="25.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="25" width="24.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="25" width="27.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="25" width="30.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="25" width="27.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="25" width="23.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="25" width="24.8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="25" width="11.53"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="F2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>242</v>
       </c>
+      <c r="C2" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="G3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>248</v>
       </c>
+      <c r="B3" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="C4" s="26" t="s">
+      <c r="A4" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="E4" s="26" t="s">
+      <c r="C4" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
+      <c r="C5" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
+      <c r="A6" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="27"/>
+      <c r="D11" s="28"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5205,7 +5288,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="10" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -5215,7 +5298,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>34</v>
@@ -5225,8 +5308,8 @@
       <c r="B4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>262</v>
+      <c r="C4" s="29" t="s">
+        <v>267</v>
       </c>
       <c r="D4" s="15"/>
     </row>
@@ -5234,8 +5317,8 @@
       <c r="B5" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>263</v>
+      <c r="C5" s="29" t="s">
+        <v>268</v>
       </c>
       <c r="D5" s="15"/>
     </row>
@@ -5243,8 +5326,8 @@
       <c r="B6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>264</v>
+      <c r="C6" s="29" t="s">
+        <v>269</v>
       </c>
       <c r="D6" s="15"/>
     </row>
@@ -5252,8 +5335,8 @@
       <c r="B7" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>265</v>
+      <c r="C7" s="29" t="s">
+        <v>270</v>
       </c>
       <c r="D7" s="15"/>
     </row>
@@ -5261,8 +5344,8 @@
       <c r="B8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>266</v>
+      <c r="C8" s="29" t="s">
+        <v>271</v>
       </c>
       <c r="D8" s="15"/>
     </row>
@@ -5270,28 +5353,28 @@
       <c r="B9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="28"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="28"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="28"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="28"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="15"/>
     </row>
   </sheetData>
@@ -5316,488 +5399,488 @@
   <dimension ref="B2:F35"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="29" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="29" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="29" width="37.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="29" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="29" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="29" width="32"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="29" width="9.14"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="30" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="37.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="30" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="30" width="25.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="30" width="32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="30" width="9.14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="30" t="n">
+      <c r="B3" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>272</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>274</v>
+      <c r="C3" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="30" t="n">
+      <c r="B4" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>278</v>
+      <c r="C4" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>279</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="E5" s="31" t="s">
+      <c r="C5" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="F5" s="31" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>284</v>
-      </c>
-      <c r="E6" s="31" t="s">
+      <c r="E10" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="D12" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="F6" s="31" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>292</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>300</v>
-      </c>
-      <c r="F10" s="31" t="s">
+      <c r="E12" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="D14" s="31" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>312</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>313</v>
+      <c r="E14" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>316</v>
+      <c r="C15" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>319</v>
+      <c r="C16" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>322</v>
+      <c r="C17" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="31" t="s">
-        <v>323</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="F18" s="31" t="s">
-        <v>326</v>
+      <c r="C18" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>329</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="E19" s="31" t="s">
+      <c r="C19" s="32" t="s">
+        <v>332</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>333</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>337</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>341</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="D22" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="F19" s="31" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="E20" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>339</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>340</v>
+      <c r="E22" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="31" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5828,55 +5911,55 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="32" t="s">
-        <v>341</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>347</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C3" s="32" t="n">
+      <c r="C3" s="33" t="n">
         <v>29</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32" t="n">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="32"/>
+      <c r="F3" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4"/>
-      <c r="C4" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D4" s="32" t="s">
+      <c r="C4" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F4" s="32" t="s">
+      <c r="E4" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F4" s="33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4"/>
       <c r="C5" s="21" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D5" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F5" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -5886,14 +5969,14 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4"/>
       <c r="C6" s="21" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D6" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="F6" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -5903,16 +5986,16 @@
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4"/>
       <c r="C7" s="21" t="s">
-        <v>348</v>
-      </c>
-      <c r="D7" s="33" t="b">
+        <v>353</v>
+      </c>
+      <c r="D7" s="34" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="F7" s="33" t="b">
+        <v>351</v>
+      </c>
+      <c r="F7" s="34" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -5920,16 +6003,16 @@
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4"/>
       <c r="C8" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="D8" s="33" t="b">
+        <v>354</v>
+      </c>
+      <c r="D8" s="34" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>348</v>
-      </c>
-      <c r="F8" s="33" t="b">
+        <v>353</v>
+      </c>
+      <c r="F8" s="34" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -5938,41 +6021,41 @@
       <c r="B9" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32" t="n">
+      <c r="D9" s="33"/>
+      <c r="E9" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="F9" s="32"/>
+      <c r="F9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4"/>
-      <c r="C10" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D10" s="32" t="s">
+      <c r="C10" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D10" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F10" s="32" t="s">
+      <c r="E10" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F10" s="33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4"/>
       <c r="C11" s="21" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D11" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F11" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -5982,14 +6065,14 @@
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4"/>
       <c r="C12" s="21" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D12" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F12" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -5999,16 +6082,16 @@
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4"/>
       <c r="C13" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="D13" s="33" t="b">
+        <v>351</v>
+      </c>
+      <c r="D13" s="34" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="F13" s="33" t="b">
+        <v>357</v>
+      </c>
+      <c r="F13" s="34" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6017,41 +6100,41 @@
       <c r="B14" s="4" t="n">
         <v>2027</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="33" t="n">
         <v>31</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32" t="n">
+      <c r="D14" s="33"/>
+      <c r="E14" s="33" t="n">
         <v>32</v>
       </c>
-      <c r="F14" s="32"/>
+      <c r="F14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4"/>
-      <c r="C15" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D15" s="32" t="s">
+      <c r="C15" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D15" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F15" s="32" t="s">
+      <c r="E15" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F15" s="33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4"/>
       <c r="C16" s="21" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D16" s="23" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F16" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6061,7 +6144,7 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4"/>
       <c r="C17" s="21" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D17" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6077,34 +6160,34 @@
       <c r="B18" s="4" t="n">
         <v>2028</v>
       </c>
-      <c r="C18" s="34" t="n">
+      <c r="C18" s="35" t="n">
         <v>32</v>
       </c>
-      <c r="D18" s="34"/>
-      <c r="E18" s="32" t="n">
+      <c r="D18" s="35"/>
+      <c r="E18" s="33" t="n">
         <v>33</v>
       </c>
-      <c r="F18" s="32"/>
+      <c r="F18" s="33"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4"/>
-      <c r="C19" s="34" t="s">
-        <v>343</v>
-      </c>
-      <c r="D19" s="32" t="s">
+      <c r="C19" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F19" s="32" t="s">
+      <c r="E19" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F19" s="33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="4"/>
-      <c r="C20" s="35" t="s">
-        <v>357</v>
+      <c r="C20" s="36" t="s">
+        <v>362</v>
       </c>
       <c r="D20" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6118,8 +6201,8 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="4"/>
-      <c r="C21" s="35" t="s">
-        <v>358</v>
+      <c r="C21" s="36" t="s">
+        <v>363</v>
       </c>
       <c r="D21" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6134,7 +6217,7 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4"/>
       <c r="C22" s="21" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D22" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6150,27 +6233,27 @@
       <c r="B23" s="4" t="n">
         <v>2029</v>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="33" t="n">
         <v>33</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32" t="n">
+      <c r="D23" s="33"/>
+      <c r="E23" s="33" t="n">
         <v>34</v>
       </c>
-      <c r="F23" s="32"/>
+      <c r="F23" s="33"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4"/>
-      <c r="C24" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D24" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F24" s="32" t="s">
+      <c r="E24" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F24" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6204,27 +6287,27 @@
       <c r="B27" s="4" t="n">
         <v>2030</v>
       </c>
-      <c r="C27" s="32" t="n">
+      <c r="C27" s="33" t="n">
         <v>34</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32" t="n">
+      <c r="D27" s="33"/>
+      <c r="E27" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="F27" s="32"/>
+      <c r="F27" s="33"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4"/>
-      <c r="C28" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D28" s="32" t="s">
+      <c r="C28" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D28" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F28" s="32" t="s">
+      <c r="E28" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F28" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6236,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F29" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6260,34 +6343,34 @@
       <c r="B31" s="4" t="n">
         <v>2031</v>
       </c>
-      <c r="C31" s="32" t="n">
+      <c r="C31" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32" t="n">
+      <c r="D31" s="33"/>
+      <c r="E31" s="33" t="n">
         <v>36</v>
       </c>
-      <c r="F31" s="32"/>
+      <c r="F31" s="33"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4"/>
-      <c r="C32" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D32" s="32" t="s">
+      <c r="C32" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D32" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F32" s="32" t="s">
+      <c r="E32" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F32" s="33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4"/>
       <c r="C33" s="21" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D33" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6316,27 +6399,27 @@
       <c r="B35" s="4" t="n">
         <v>2032</v>
       </c>
-      <c r="C35" s="32" t="n">
+      <c r="C35" s="33" t="n">
         <v>36</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32" t="n">
+      <c r="D35" s="33"/>
+      <c r="E35" s="33" t="n">
         <v>37</v>
       </c>
-      <c r="F35" s="32"/>
+      <c r="F35" s="33"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4"/>
-      <c r="C36" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D36" s="32" t="s">
+      <c r="C36" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D36" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F36" s="32" t="s">
+      <c r="E36" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F36" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6370,27 +6453,27 @@
       <c r="B39" s="4" t="n">
         <v>2033</v>
       </c>
-      <c r="C39" s="32" t="n">
+      <c r="C39" s="33" t="n">
         <v>37</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32" t="n">
+      <c r="D39" s="33"/>
+      <c r="E39" s="33" t="n">
         <v>38</v>
       </c>
-      <c r="F39" s="32"/>
+      <c r="F39" s="33"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4"/>
-      <c r="C40" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D40" s="32" t="s">
+      <c r="C40" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D40" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F40" s="32" t="s">
+      <c r="E40" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F40" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6424,27 +6507,27 @@
       <c r="B43" s="4" t="n">
         <v>2034</v>
       </c>
-      <c r="C43" s="32" t="n">
+      <c r="C43" s="33" t="n">
         <v>38</v>
       </c>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32" t="n">
+      <c r="D43" s="33"/>
+      <c r="E43" s="33" t="n">
         <v>39</v>
       </c>
-      <c r="F43" s="32"/>
+      <c r="F43" s="33"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4"/>
-      <c r="C44" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D44" s="32" t="s">
+      <c r="C44" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D44" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F44" s="32" t="s">
+      <c r="E44" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F44" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6478,27 +6561,27 @@
       <c r="B47" s="4" t="n">
         <v>2035</v>
       </c>
-      <c r="C47" s="32" t="n">
+      <c r="C47" s="33" t="n">
         <v>39</v>
       </c>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32" t="n">
+      <c r="D47" s="33"/>
+      <c r="E47" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="F47" s="32"/>
+      <c r="F47" s="33"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4"/>
-      <c r="C48" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D48" s="32" t="s">
+      <c r="C48" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D48" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E48" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F48" s="32" t="s">
+      <c r="E48" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F48" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6510,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="F49" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6534,34 +6617,34 @@
       <c r="B51" s="4" t="n">
         <v>2036</v>
       </c>
-      <c r="C51" s="32" t="n">
+      <c r="C51" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32" t="n">
+      <c r="D51" s="33"/>
+      <c r="E51" s="33" t="n">
         <v>41</v>
       </c>
-      <c r="F51" s="32"/>
+      <c r="F51" s="33"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4"/>
-      <c r="C52" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D52" s="32" t="s">
+      <c r="C52" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D52" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E52" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F52" s="32" t="s">
+      <c r="E52" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F52" s="33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="4"/>
       <c r="C53" s="21" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D53" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6590,27 +6673,27 @@
       <c r="B55" s="4" t="n">
         <v>2037</v>
       </c>
-      <c r="C55" s="32" t="n">
+      <c r="C55" s="33" t="n">
         <v>41</v>
       </c>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32" t="n">
+      <c r="D55" s="33"/>
+      <c r="E55" s="33" t="n">
         <v>42</v>
       </c>
-      <c r="F55" s="32"/>
+      <c r="F55" s="33"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="4"/>
-      <c r="C56" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D56" s="32" t="s">
+      <c r="C56" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D56" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E56" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F56" s="32" t="s">
+      <c r="E56" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F56" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6644,27 +6727,27 @@
       <c r="B59" s="4" t="n">
         <v>2038</v>
       </c>
-      <c r="C59" s="32" t="n">
+      <c r="C59" s="33" t="n">
         <v>42</v>
       </c>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32" t="n">
+      <c r="D59" s="33"/>
+      <c r="E59" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="F59" s="32"/>
+      <c r="F59" s="33"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4"/>
-      <c r="C60" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D60" s="32" t="s">
+      <c r="C60" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D60" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E60" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F60" s="32" t="s">
+      <c r="E60" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F60" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6698,27 +6781,27 @@
       <c r="B63" s="4" t="n">
         <v>2039</v>
       </c>
-      <c r="C63" s="32" t="n">
+      <c r="C63" s="33" t="n">
         <v>43</v>
       </c>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32" t="n">
-        <v>44</v>
-      </c>
-      <c r="F63" s="32"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="F63" s="33"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4"/>
-      <c r="C64" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D64" s="32" t="s">
+      <c r="C64" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D64" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E64" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F64" s="32" t="s">
+      <c r="E64" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F64" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6752,27 +6835,27 @@
       <c r="B67" s="4" t="n">
         <v>2040</v>
       </c>
-      <c r="C67" s="32" t="n">
-        <v>44</v>
-      </c>
-      <c r="D67" s="32"/>
-      <c r="E67" s="32" t="n">
+      <c r="C67" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="D67" s="33"/>
+      <c r="E67" s="33" t="n">
         <v>45</v>
       </c>
-      <c r="F67" s="32"/>
+      <c r="F67" s="33"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4"/>
-      <c r="C68" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D68" s="32" t="s">
+      <c r="C68" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D68" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E68" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F68" s="32" t="s">
+      <c r="E68" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F68" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -6784,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="21" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="F69" s="23" t="b">
         <f aca="false">FALSE()</f>
@@ -6808,34 +6891,34 @@
       <c r="B71" s="4" t="n">
         <v>2041</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C71" s="33" t="n">
         <v>45</v>
       </c>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32" t="n">
+      <c r="D71" s="33"/>
+      <c r="E71" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="F71" s="32"/>
+      <c r="F71" s="33"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4"/>
-      <c r="C72" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="D72" s="32" t="s">
+      <c r="C72" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="D72" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E72" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="F72" s="32" t="s">
+      <c r="E72" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="F72" s="33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4"/>
       <c r="C73" s="21" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D73" s="23" t="b">
         <f aca="false">FALSE()</f>
